--- a/artfynd/A 63575-2023 artfynd.xlsx
+++ b/artfynd/A 63575-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128816568</v>
       </c>
       <c r="B2" t="n">
-        <v>58406</v>
+        <v>58433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128816563</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>128816586</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>128816564</v>
       </c>
       <c r="B5" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63575-2023 artfynd.xlsx
+++ b/artfynd/A 63575-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128816568</v>
       </c>
       <c r="B2" t="n">
-        <v>58433</v>
+        <v>58437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128816563</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>128816586</v>
       </c>
       <c r="B4" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>128816564</v>
       </c>
       <c r="B5" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63575-2023 artfynd.xlsx
+++ b/artfynd/A 63575-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128816568</v>
       </c>
       <c r="B2" t="n">
-        <v>58437</v>
+        <v>58440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128816563</v>
       </c>
       <c r="B3" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>128816586</v>
       </c>
       <c r="B4" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>128816564</v>
       </c>
       <c r="B5" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63575-2023 artfynd.xlsx
+++ b/artfynd/A 63575-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128816568</v>
       </c>
       <c r="B2" t="n">
-        <v>58440</v>
+        <v>58442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128816563</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>128816586</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>128816564</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63575-2023 artfynd.xlsx
+++ b/artfynd/A 63575-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128816568</v>
       </c>
       <c r="B2" t="n">
-        <v>58442</v>
+        <v>58444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>128816563</v>
       </c>
       <c r="B3" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>128816586</v>
       </c>
       <c r="B4" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>128816564</v>
       </c>
       <c r="B5" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 63575-2023 artfynd.xlsx
+++ b/artfynd/A 63575-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128816568</v>
+        <v>114437940</v>
       </c>
       <c r="B2" t="n">
-        <v>58444</v>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mossekant 1, N om Funtamosse, Vg</t>
+          <t>Viseås, norr om, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>342769</v>
+        <v>342580</v>
       </c>
       <c r="R2" t="n">
-        <v>6435573</v>
+        <v>6435635</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>07:50</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>07:50</t>
+          <t>2024-01-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mindre tuva, i bäckdal.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,32 +763,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128816563</v>
+        <v>128816561</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,7 +815,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -883,11 +871,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>07:50</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spillkråkehack i död tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,57 +897,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128816586</v>
+        <v>128816647</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr om mossen1, N om Funtamosse, Vg</t>
+          <t>Skogsbilväg 6, N om Funtamosse, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>342912</v>
+        <v>342761</v>
       </c>
       <c r="R4" t="n">
-        <v>6435535</v>
+        <v>6435594</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -991,27 +970,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 4.</t>
+          <t>Spillkråkehack i död tall, norrsidan om vägen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,7 +1020,7 @@
         <v>128816564</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,6 +1133,361 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128816586</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norr om mossen1, N om Funtamosse, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>342912</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6435535</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minst 4.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128816568</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mossekant 1, N om Funtamosse, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>342769</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6435573</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114437910</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Viseås, norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>342580</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6435635</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-01-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-01-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt, på klenare gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63575-2023 artfynd.xlsx
+++ b/artfynd/A 63575-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114437940</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128816561</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128816647</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1133,6 +1153,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128816564</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128816586</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1376,6 +1406,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128816568</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1488,8 +1523,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114437910</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>